--- a/maintenance_forms/011_warranty_tracking_dashboard--maintenance_forms.xlsx
+++ b/maintenance_forms/011_warranty_tracking_dashboard--maintenance_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -878,12 +878,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>claim_resolution_date</t>
+          <t>claim_resolution_date_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>claim-resolution-date</t>
+          <t>Claim Resolution Date 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -901,12 +901,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>claim_resolution_time</t>
+          <t>claim_resolution_time_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>claim-resolution-time</t>
+          <t>Claim Resolution Time 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -924,12 +924,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>resolution_notes</t>
+          <t>resolution_notes_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>resolution-notes</t>
+          <t>Resolution Notes 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
